--- a/data/trans_dic/P34B02_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,17</t>
+          <t>2,7; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,28</t>
+          <t>2,49; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,42</t>
+          <t>6,2; 10,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,93</t>
+          <t>1,41; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,72</t>
+          <t>2,37; 4,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,82</t>
+          <t>4,11; 6,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,54</t>
+          <t>2,15; 3,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,52</t>
+          <t>2,76; 4,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,73</t>
+          <t>5,34; 7,86</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,69</t>
+          <t>4,74; 6,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 9,06</t>
+          <t>6,74; 9,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 22,61</t>
+          <t>13,37; 22,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,54</t>
+          <t>3,42; 5,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,6</t>
+          <t>4,58; 6,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,5</t>
+          <t>8,81; 14,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,76</t>
+          <t>4,44; 5,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,54</t>
+          <t>5,93; 7,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,89; 18,08</t>
+          <t>12,59; 18,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,47</t>
+          <t>5,3; 10,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,77</t>
+          <t>8,86; 14,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,64; 25,89</t>
+          <t>18,59; 25,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,61</t>
+          <t>4,17; 9,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,46</t>
+          <t>5,62; 10,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 24,4</t>
+          <t>18,48; 24,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,9</t>
+          <t>5,38; 8,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 11,65</t>
+          <t>8,09; 11,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 23,97</t>
+          <t>19,45; 24,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,17</t>
+          <t>4,61; 6,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,55</t>
+          <t>6,62; 8,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,31</t>
+          <t>14,14; 20,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,55</t>
+          <t>3,1; 4,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,08</t>
+          <t>4,54; 6,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,07</t>
+          <t>10,15; 13,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,12</t>
+          <t>4,09; 5,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,11</t>
+          <t>5,83; 7,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 16,64</t>
+          <t>13,33; 16,66</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24591; 50297</t>
+          <t>26272; 50676</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18795; 39794</t>
+          <t>18774; 39936</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31291; 53678</t>
+          <t>31929; 55294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18741; 39262</t>
+          <t>18900; 39404</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23825; 46998</t>
+          <t>23565; 47656</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31112; 51278</t>
+          <t>30921; 51347</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49299; 81888</t>
+          <t>49665; 82290</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47701; 78993</t>
+          <t>48225; 81866</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67092; 97948</t>
+          <t>67626; 99558</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91861; 131361</t>
+          <t>93095; 129065</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>136863; 188044</t>
+          <t>139869; 188911</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>300165; 516743</t>
+          <t>305614; 522147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61708; 97361</t>
+          <t>60096; 94331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89944; 131177</t>
+          <t>91086; 132097</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>206000; 324132</t>
+          <t>197022; 325986</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161467; 214421</t>
+          <t>165298; 216813</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240035; 306426</t>
+          <t>240989; 306935</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>582867; 817565</t>
+          <t>569453; 818394</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25323; 50374</t>
+          <t>25500; 49364</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49251; 80798</t>
+          <t>48454; 81120</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120500; 167427</t>
+          <t>120180; 164790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20021; 44082</t>
+          <t>19141; 43439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30234; 57425</t>
+          <t>30854; 55590</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>121971; 161151</t>
+          <t>122046; 160054</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49196; 83685</t>
+          <t>50561; 84135</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87680; 127689</t>
+          <t>88656; 129891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>252876; 313363</t>
+          <t>254196; 317927</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>156134; 211008</t>
+          <t>157442; 210404</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>225571; 288673</t>
+          <t>223432; 291072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>497845; 700163</t>
+          <t>487524; 700100</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112247; 161713</t>
+          <t>110106; 160684</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>159823; 214646</t>
+          <t>160258; 214827</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>382784; 513232</t>
+          <t>370325; 507778</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>284411; 357103</t>
+          <t>285157; 358090</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>403531; 490941</t>
+          <t>402533; 484886</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>949570; 1180385</t>
+          <t>945629; 1182452</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B02_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,21</t>
+          <t>2,6; 5,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,29</t>
+          <t>2,52; 5,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,74</t>
+          <t>6,6; 11,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,95</t>
+          <t>1,44; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,79</t>
+          <t>2,34; 4,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,83</t>
+          <t>4,03; 6,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,56</t>
+          <t>2,14; 3,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,68</t>
+          <t>2,71; 4,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,86</t>
+          <t>5,58; 8,04</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,57</t>
+          <t>4,68; 6,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,1</t>
+          <t>6,66; 9,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 22,85</t>
+          <t>19,63; 24,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,37</t>
+          <t>3,43; 5,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,64</t>
+          <t>4,57; 6,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 14,58</t>
+          <t>13,07; 15,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,83</t>
+          <t>4,35; 5,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,55</t>
+          <t>6,03; 7,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 18,1</t>
+          <t>16,81; 19,54</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,26</t>
+          <t>5,38; 10,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 14,83</t>
+          <t>9,11; 15,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 25,48</t>
+          <t>18,26; 25,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 9,47</t>
+          <t>4,24; 9,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,12</t>
+          <t>5,71; 10,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,48; 24,23</t>
+          <t>18,09; 23,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,95</t>
+          <t>5,35; 9,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,85</t>
+          <t>7,86; 11,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,32</t>
+          <t>18,82; 23,3</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,16</t>
+          <t>4,65; 6,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,62</t>
+          <t>6,59; 8,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 20,31</t>
+          <t>18,04; 21,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,52</t>
+          <t>3,19; 4,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,08</t>
+          <t>4,51; 6,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,92</t>
+          <t>12,59; 14,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,14</t>
+          <t>4,08; 5,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,02</t>
+          <t>5,78; 6,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 16,66</t>
+          <t>15,58; 17,5</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41860</t>
+          <t>50617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81577</t>
+          <t>92883</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26272; 50676</t>
+          <t>25306; 50419</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18774; 39936</t>
+          <t>19003; 39202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31929; 55294</t>
+          <t>38173; 65753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18900; 39404</t>
+          <t>19327; 40171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23565; 47656</t>
+          <t>23229; 47654</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30921; 51347</t>
+          <t>33021; 53708</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49665; 82290</t>
+          <t>49449; 82751</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48225; 81866</t>
+          <t>47342; 78979</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67626; 99558</t>
+          <t>78079; 112411</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445540</t>
+          <t>484961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>279094</t>
+          <t>312377</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>724634</t>
+          <t>797338</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93095; 129065</t>
+          <t>91947; 133344</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139869; 188911</t>
+          <t>138304; 189853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>305614; 522147</t>
+          <t>436958; 534306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60096; 94331</t>
+          <t>60188; 96160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91086; 132097</t>
+          <t>90810; 132826</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>197022; 325986</t>
+          <t>283242; 344073</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165298; 216813</t>
+          <t>161687; 218258</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240989; 306935</t>
+          <t>244900; 310165</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>569453; 818394</t>
+          <t>738506; 858137</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142494</t>
+          <t>152442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>150877</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>283680</t>
+          <t>303318</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25500; 49364</t>
+          <t>25882; 49876</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48454; 81120</t>
+          <t>49827; 82134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120180; 164790</t>
+          <t>129922; 179042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19141; 43439</t>
+          <t>19451; 44468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30854; 55590</t>
+          <t>31345; 55556</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>122046; 160054</t>
+          <t>132905; 174272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50561; 84135</t>
+          <t>50278; 84901</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88656; 129891</t>
+          <t>86113; 128622</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>254196; 317927</t>
+          <t>272267; 336986</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629893</t>
+          <t>688019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>459998</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1089891</t>
+          <t>1193539</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157442; 210404</t>
+          <t>158847; 211258</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>223432; 291072</t>
+          <t>222467; 286949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>487524; 700100</t>
+          <t>634291; 748261</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110106; 160684</t>
+          <t>113178; 162116</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>160258; 214827</t>
+          <t>159308; 212145</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>370325; 507778</t>
+          <t>468738; 544908</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>285157; 358090</t>
+          <t>284261; 357862</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>402533; 484886</t>
+          <t>399668; 482246</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>945629; 1182452</t>
+          <t>1127295; 1266741</t>
         </is>
       </c>
     </row>
